--- a/outputs/evaluation/decision/v2/CF_M01/run_3/CF_M01_decision_eval_gt_report.xlsx
+++ b/outputs/evaluation/decision/v2/CF_M01/run_3/CF_M01_decision_eval_gt_report.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:J2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -504,110 +504,16 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>AD_04</t>
+          <t>AD_02</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>The business layer and the data layer are divided into several different services to improve the security, scalability, and availability of the system.</t>
+          <t>The platform lacks an efficient storage system that allows saving all necessary data on a large scale and a system that allows us to obtain and analyze this data. The objective of this is to improve the security, scalability and availability of the system.</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>0.6377</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>CF_M01_AD04</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>The decision was made to use AWS and not other cloud services due to its low price and its previous use by the company.</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>*CF_M01_C09, *CF_M01_C10</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>CF_M01_AU16</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>46</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Price; Experience</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>AWS cloud services set</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>AD_02</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>AWS is used for infrastructure because it allows the creation of scalable and highly available applications.</t>
-        </is>
-      </c>
-      <c r="J3" t="n">
-        <v>0.6629</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>CF_M01_AD07</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>To ensure the fastest possible data transmission, two Amazon services have been used, which allow us to perform a transmission in almost real time.</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>CF_M01_C01</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>CF_M01_AU16</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Speed and latency</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>AWS cloud services set</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>AD_02</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>AWS is used for infrastructure because it allows the creation of scalable and highly available applications.</t>
-        </is>
-      </c>
-      <c r="J4" t="n">
-        <v>0.6732</v>
+        <v>0.6279</v>
       </c>
     </row>
   </sheetData>
